--- a/event_registration_forms/008_labor_law_seminar_registration_form--event_registration_forms.xlsx
+++ b/event_registration_forms/008_labor_law_seminar_registration_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option':_'alabama'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option': 'Alabama'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option':_'alaska'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option': 'Alaska'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_'arizona'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': 'Arizona'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_'arkansas'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': 'Arkansas'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'california'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'California'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_'colorado'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 'Colorado'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_'connecticut'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 'Connecticut'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_'delaware'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 'Delaware'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_'florida'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': 'Florida'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'georgia'}</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 'Georgia'}</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_'hawaii'}</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': 'Hawaii'}</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_'idaho'}</t>
+          <t>option_12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': 'Idaho'}</t>
+          <t>Option 12</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_'illinois'}</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': 'Illinois'}</t>
+          <t>Option 13</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option':_'indiana'}</t>
+          <t>option_14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option': 'Indiana'}</t>
+          <t>Option 14</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option':_'iowa'}</t>
+          <t>option_15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option': 'Iowa'}</t>
+          <t>Option 15</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option':_'kansas'}</t>
+          <t>option_16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option': 'Kansas'}</t>
+          <t>Option 16</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option':_'kentucky'}</t>
+          <t>option_17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option': 'Kentucky'}</t>
+          <t>Option 17</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option':_'louisiana'}</t>
+          <t>option_18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option': 'Louisiana'}</t>
+          <t>Option 18</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option':_'maine'}</t>
+          <t>option_19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option': 'Maine'}</t>
+          <t>Option 19</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option':_'maryland'}</t>
+          <t>option_20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option': 'Maryland'}</t>
+          <t>Option 20</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option':_'massachusetts'}</t>
+          <t>option_21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option': 'Massachusetts'}</t>
+          <t>Option 21</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option':_'michigan'}</t>
+          <t>option_22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option': 'Michigan'}</t>
+          <t>Option 22</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option':_'minnesota'}</t>
+          <t>option_23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option': 'Minnesota'}</t>
+          <t>Option 23</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option':_'mississippi'}</t>
+          <t>option_24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option': 'Mississippi'}</t>
+          <t>Option 24</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option':_'missouri'}</t>
+          <t>option_25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option': 'Missouri'}</t>
+          <t>Option 25</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'option':_'montana'}</t>
+          <t>option_26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'option': 'Montana'}</t>
+          <t>Option 26</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option':_'nebraska'}</t>
+          <t>option_27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option': 'Nebraska'}</t>
+          <t>Option 27</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'option':_'nevada'}</t>
+          <t>option_28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'option': 'Nevada'}</t>
+          <t>Option 28</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'option':_'new_hampshire'}</t>
+          <t>option_29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'option': 'New Hampshire'}</t>
+          <t>Option 29</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'option':_'new_mexico'}</t>
+          <t>option_30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'option': 'New Mexico'}</t>
+          <t>Option 30</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'option':_'new_york'}</t>
+          <t>option_31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'option': 'New York'}</t>
+          <t>Option 31</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'option':_'north_carolina'}</t>
+          <t>option_32</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'option': 'North Carolina'}</t>
+          <t>Option 32</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'option':_'north_dakota'}</t>
+          <t>option_33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'option': 'North Dakota'}</t>
+          <t>Option 33</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'option':_'ohio'}</t>
+          <t>option_34</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'option': 'Ohio'}</t>
+          <t>Option 34</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'option':_'oklahoma'}</t>
+          <t>option_35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'option': 'Oklahoma'}</t>
+          <t>Option 35</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'option':_'oregon'}</t>
+          <t>option_36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'option': 'Oregon'}</t>
+          <t>Option 36</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'option':_'pennsylvania'}</t>
+          <t>option_37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'option': 'Pennsylvania'}</t>
+          <t>Option 37</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'option':_'rhode_island'}</t>
+          <t>option_38</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'option': 'Rhode Island'}</t>
+          <t>Option 38</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'option':_'south_carolina'}</t>
+          <t>option_39</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'option': 'South Carolina'}</t>
+          <t>Option 39</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'option':_'south_dakota'}</t>
+          <t>option_40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'option': 'South Dakota'}</t>
+          <t>Option 40</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'option':_'tennessee'}</t>
+          <t>option_41</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'option': 'Tennessee'}</t>
+          <t>Option 41</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'option':_'texas'}</t>
+          <t>option_42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'option': 'Texas'}</t>
+          <t>Option 42</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'option':_'utah'}</t>
+          <t>option_43</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'option': 'Utah'}</t>
+          <t>Option 43</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'option':_'vermont'}</t>
+          <t>option_44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'option': 'Vermont'}</t>
+          <t>Option 44</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'option':_'virginia'}</t>
+          <t>option_45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'option': 'Virginia'}</t>
+          <t>Option 45</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'option':_'washington'}</t>
+          <t>option_46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'option': 'Washington'}</t>
+          <t>Option 46</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'option':_'west_virginia'}</t>
+          <t>option_47</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'option': 'West Virginia'}</t>
+          <t>Option 47</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'option':_'wisconsin'}</t>
+          <t>option_48</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'option': 'Wisconsin'}</t>
+          <t>Option 48</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'option':_'wyoming'}</t>
+          <t>option_49</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'option': 'Wyoming'}</t>
+          <t>Option 49</t>
         </is>
       </c>
     </row>
@@ -1665,12 +1665,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'option':_'in-person'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'option': 'In-person'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'option':_'virtual'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'option': 'Virtual'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'option':_'maybe'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'option': 'Maybe'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
